--- a/generate_dashboard_使用说明.xlsx
+++ b/generate_dashboard_使用说明.xlsx
@@ -84,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -106,11 +106,55 @@
         <color rgb="00D9DEE7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9DEE7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9DEE7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9DEE7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9DEE7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9DEE7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9DEE7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9DEE7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9DEE7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -135,6 +179,8 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -513,7 +559,7 @@
           <t>generate_dashboard.py 脚本使用说明</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="10" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -619,7 +665,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>22个数据维度，覆盖项目、合同、人力、进度、预警等</t>
+          <t>20个数据维度，覆盖项目、合同、人力、进度、预警等</t>
         </is>
       </c>
     </row>
@@ -679,12 +725,12 @@
           <t>输入文件规范（4个必填源数据文件）</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="10" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -893,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -910,11 +956,11 @@
           <t>输出文件：看板.html 模块清单</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="10" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1104,27 +1150,27 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>项目进度分布</t>
+          <t>人员工作饱和度分析</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>柱状图</t>
+          <t>统计数字+饼图</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>项目数据表.xlsx</t>
+          <t>人力投入表.xlsx</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>项目进度&gt;0</t>
+          <t>所属中心="数智技术服务中心"</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>6个进度区间分布（排除0值）</t>
+          <t>在岗/未投入人员数、整体饱和度、饱和度分布</t>
         </is>
       </c>
     </row>
@@ -1134,27 +1180,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>本月部门人力投入</t>
+          <t>部门工时投入对比</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>横向柱状图</t>
+          <t>分组柱状图</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>项目数据表.xlsx</t>
+          <t>人力投入表.xlsx</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>本月投入&gt;0 且 所属部门∈数智技术服务中心</t>
+          <t>所属中心="数智技术服务中心"</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>按部门汇总本月投入人月</t>
+          <t>各部门实际工时 vs 应投入工时</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1210,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>人员工作饱和度分析</t>
+          <t>部门人均工作饱和度</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>统计数字+饼图</t>
+          <t>渐变色横向柱状图</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1184,7 +1230,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>在岗/未投入人员数、整体饱和度、饱和度分布</t>
+          <t>按部门计算人均饱和度，颜色按阈值渐变</t>
         </is>
       </c>
     </row>
@@ -1194,27 +1240,27 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>部门工时投入对比</t>
+          <t>本期人力投入TOP10项目</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>分组柱状图</t>
+          <t>堆叠柱状图</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>人力投入表.xlsx</t>
+          <t>本期人力投入项目情况.xlsx</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>所属中心="数智技术服务中心"</t>
+          <t>按总投入降序TOP10</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>各部门实际工时 vs 应投入工时</t>
+          <t>按部门着色的堆叠柱状图</t>
         </is>
       </c>
     </row>
@@ -1224,27 +1270,27 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>部门人均工作饱和度</t>
+          <t>各部门人力投入TOP3项目</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>渐变色横向柱状图</t>
+          <t>四列卡片布局</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>人力投入表.xlsx</t>
+          <t>本期人力投入项目情况.xlsx</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>所属中心="数智技术服务中心"</t>
+          <t>各部门投入&gt;0</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>按部门计算人均饱和度，颜色按阈值渐变</t>
+          <t>智能部/政务部/大数据部/产品创新部各TOP3</t>
         </is>
       </c>
     </row>
@@ -1254,27 +1300,27 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>本期人力投入TOP10项目</t>
+          <t>本期项目变化动态</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>堆叠柱状图</t>
+          <t>表格（新增+延期）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况.xlsx</t>
+          <t>本期项目变化情况.xlsx</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>按总投入降序TOP10</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>按部门着色的堆叠柱状图</t>
+          <t>按类型分为新增项目和延期项目</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1330,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>各部门人力投入TOP3项目</t>
+          <t>项目超期/到期预警</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>四列卡片布局</t>
+          <t>表格（超期+到期）</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1299,12 +1345,12 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>各部门投入&gt;0</t>
+          <t>禅道状态含"超期"或"还有X天"且≤60天</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>智能部/政务部/大数据部/产品创新部各TOP3</t>
+          <t>已超期项目和60天内到期项目</t>
         </is>
       </c>
     </row>
@@ -1314,17 +1360,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>本期项目变化动态</t>
+          <t>合同金额TOP10项目</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>表格（新增+延期）</t>
+          <t>表格</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>本期项目变化情况.xlsx</t>
+          <t>项目数据表.xlsx</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1334,7 +1380,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>按类型分为新增项目和延期项目</t>
+          <t>按合同金额降序前10</t>
         </is>
       </c>
     </row>
@@ -1344,27 +1390,27 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>项目超期/到期预警</t>
+          <t>人力投入累计TOP10项目</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>表格（超期+到期）</t>
+          <t>表格</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>本期人力投入项目情况.xlsx</t>
+          <t>项目数据表.xlsx</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>禅道状态含"超期"或"还有X天"且≤60天</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>已超期项目和60天内到期项目</t>
+          <t>按累计投入人月降序前10</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1420,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>合同金额TOP10项目</t>
+          <t>本期人力投入项目明细</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>表格</t>
+          <t>表格（按部门拆分）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>项目数据表.xlsx</t>
+          <t>本期人力投入项目情况.xlsx</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1394,7 +1440,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>按合同金额降序前10</t>
+          <t>全部项目按总投入降序排列</t>
         </is>
       </c>
     </row>
@@ -1404,85 +1450,25 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>人力投入累计TOP10项目</t>
+          <t>挂起项目 + 低饱和度人员</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>表格</t>
+          <t>双表格</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>项目数据表.xlsx</t>
+          <t>项目数据表.xlsx + 人力投入表.xlsx</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>挂起:项目阶段="挂起"; 低饱和:饱和度&lt;50%且在岗</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>按累计投入人月降序前10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>本期人力投入项目明细</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>表格（按部门拆分）</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>本期人力投入项目情况.xlsx</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>全部项目按总投入降序排列</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>挂起项目 + 低饱和度人员</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>双表格</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>项目数据表.xlsx + 人力投入表.xlsx</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>挂起:项目阶段="挂起"; 低饱和:饱和度&lt;50%且在岗</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>左侧挂起项目，右侧低饱和度人员</t>
         </is>
@@ -1516,8 +1502,8 @@
           <t>使用说明</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -1525,8 +1511,8 @@
           <t>一、环境准备</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1596,8 +1582,8 @@
           <t>二、生成看板</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1682,8 +1668,8 @@
           <t>三、数据更新流程</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1776,8 +1762,8 @@
           <t>四、注意事项</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
